--- a/output/workbooks/GenosAI_OrganicLeads.xlsx
+++ b/output/workbooks/GenosAI_OrganicLeads.xlsx
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q15"/>
+  <dimension ref="A1:Q17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1805,6 +1805,172 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Home Seekers</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Thomas Potgieter</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder &amp; Managing Director</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>info@homeseeker.co.za</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>+27 012 880 3127</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.homeseeker.co.za/</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/thomas-potgieter-a4972b96/</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Pretoria</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng, South Africa</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>Real Estate</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>Organic/Manual</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>Pending Send</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>HomeSeeker_Audit_GenosAI.pptx</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t>WhatsApp AI for buyer inquiries (24/7 response + viewing booking); lead routing from Property24/Private Property to agents; FICA compliance document collection workflow; agent recruitment intake automation (agents.homeseeker.co.za); buyer nurture drip for non-converting inquiries; post-sale review request sequence</t>
+        </is>
+      </c>
+      <c r="Q16" s="3" t="inlineStr">
+        <is>
+          <t>Fixed-fee platform — agents keep 100% commission. Founded 2025. 416+ active listings. Ice-breaker: Rode Potgieter 8 deals / R11.44M Oct 2025 (LinkedIn). Co-LinkedIn: linkedin.com/company/home-seekers-sa</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Swisszaco Estates</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>+2348101658350</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>https://swisszacoestates.com/</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/swisscazo-estate/about/</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>Real Estate Development</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>Organic/LinkedIn</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>Contact TBD — LinkedIn Pending</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>output/decks/SwisszacoEstates_Audit_GenosAI.pptx</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t>WhatsApp AI buyer agent (property inquiry + site visit booking); agent network recruitment automation (intake, onboarding, nurture); lead nurture sequences (re-engagement + new listing alerts); post-handover review and testimonial collection; diaspora investor nurture (UK/US/Canada) via WhatsApp</t>
+        </is>
+      </c>
+      <c r="Q17" s="3" t="inlineStr">
+        <is>
+          <t>Contact TBD — outreach via company LinkedIn page. Score 3/10, HIGH priority.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:Q1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1817,7 +1983,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2379,6 +2545,105 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Home Seekers</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Thomas Potgieter</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>info@homeseeker.co.za</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>416 listings and buyer inquiries waiting while agents are at viewings</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Hi Thomas,
+Saw the LinkedIn post on Rode's October run — 8 deals for R11.44M on a 100%-commission model. That number makes the platform's value proposition more credible than any recruitment copy.
+The question it raised for me: when a buyer submits an inquiry on one of your 416 listings at 9pm on a Sunday, what happens to that lead before Monday morning? In South Africa's market, that buyer has already sent the same inquiry to three other agents on Property24. The one who responds on WhatsApp first — even if it's an AI — controls the conversation.
+Genos AI builds WhatsApp automation specifically for real estate platforms. For HomeSeeker's model:
+WhatsApp AI for buyer inquiries — responds 24/7, answers property questions, qualifies budget and timeline, books the viewing without the agent being online. Lead goes from Property24 to confirmed appointment automatically.
+Lead routing by area and type — inquiry captured via WhatsApp, AI qualifies the buyer, assigns to the right agent based on property type and location, logged in your system.
+FICA and compliance document collection — for your back-office platform, an AI workflow that requests, follows up, and confirms receipt of required documents from buyers and sellers. Agents stop chasing paper manually.
+Agent recruitment intake — agents.homeseeker.co.za gets an AI that screens applicants, asks qualifying questions, and schedules intro calls. You're not reading every enquiry manually.
+I'm Rohan Malik, CEO of Genos AI. We build AI automation for real estate operations — WhatsApp agents, lead qualification flows, compliance automations. Happy to show you how it works in 20 minutes.
+Rohan Malik
+CEO, Genos AI
++91 638-714-2699  |  hello@genosai.tech  |  www.genosai.tech</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Hi Thomas, following up on my last message. The core gap — buyer inquiries on your 416 listings sitting unanswered while agents are at viewings — is the fastest to close. A WhatsApp AI agent for Home Seekers is typically live in under 2 weeks. Happy to walk through it in 20 minutes. — Rohan | Genos AI</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Thomas, last one from me. On a 100%-commission platform, an agent's income depends entirely on their lead conversion speed. An AI that ensures no buyer inquiry goes unanswered — even at 9pm on a Sunday — is the infrastructure that makes your agents more productive than any franchise competitor. Leaving this here if the timing isn't right. — Rohan | Genos AI</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Swisszaco Estates</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Swisszaco's agent network and a property inquiry process still stuck on contact forms</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Hi,
+Came across Swisszaco Estates while researching real estate developers in Nigeria. CAC-registered since March 2012 — 13 years in the market across construction, estate development, architectural design, and urban development. The agent network program stood out as an indicator the business is actively scaling.
+One gap that showed up immediately on swisszacoestates.com: there's no way for a property buyer or investor to get a fast response outside business hours. The contact form is the only entry point — no chat widget, no WhatsApp integration, no booking flow for property viewings. In the Nigerian market, where most buyers are comparing 3-4 developers simultaneously and expect a WhatsApp reply within the hour, a contact form with a 24-48 hour turnaround quietly hands those leads to whoever responds first.
+The same applies to your agent network. Agents researching whether to join need immediate answers on commission structure, available projects, and onboarding — a contact form puts that decision on hold.
+What we build for real estate developers at Genos AI: WhatsApp AI agents that qualify buyers (property type, location, budget, timeline), book site visits automatically, and route hot leads to the right agent — 24/7, no manual handling. We also build agent recruitment flows that capture and nurture new agent sign-ups without your team chasing each one.
+I'm Rohan Malik, CEO of Genos AI. Did a full audit of swisszacoestates.com — happy to share it or walk through it in 15 minutes.
+Rohan Malik
+CEO, Genos AI
++91 638-714-2699  |  hello@genosai.tech  |  www.genosai.tech</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>Hi, following up on my last message. The core gap — property inquiries hitting a static contact form while competitors respond on WhatsApp in minutes — is the fastest thing to fix. A WhatsApp AI agent for Swisszaco is typically live within 2 weeks. Happy to show you exactly how it works in 15 minutes. — Rohan | Genos AI</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Last one from me. The Swisszaco audit covers the WhatsApp buyer qualification flow, agent recruitment automation, and the property viewing booking system specifically. If the timing isn't right, no problem — leaving it here in case it's useful later. — Rohan | Genos AI</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2391,7 +2656,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2854,6 +3119,98 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Home Seekers</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Thomas Potgieter</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>info@homeseeker.co.za</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Real Estate</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Email Pending</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>Send cold email — pitch AI automation</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Swisszaco Estates</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Real Estate Development</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>Contact TBD</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>Source contact via LinkedIn — send cold email + deck</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>$3,000 - $6,000</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:J1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/workbooks/GenosAI_OrganicLeads.xlsx
+++ b/output/workbooks/GenosAI_OrganicLeads.xlsx
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q17"/>
+  <dimension ref="A1:Q24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1971,6 +1971,583 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>24/7 Security Services</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>David De Lima</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>info@24-7security.co.za</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>+27 011 444 2237</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>https://24-7security.co.za/</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/david-de-lima-696ba99/</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>Johannesburg</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng, South Africa</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>Security Services</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>Organic/Manual</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>Pending Send</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>24-7Security_Audit_GenosAI.pptx</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t>WhatsApp AI for prospect inquiries (24/7 quote capture + site assessment scheduling); automated quote generation from security site assessment inputs; guard shift scheduling and attendance automation via WhatsApp; PSIRA certification renewal reminders per guard; automated monthly security activity and incident reports to clients; client onboarding automation (contract to deployment to handover); lead nurture sequences for prospects who inquired but didn't convert</t>
+        </is>
+      </c>
+      <c r="Q18" s="3" t="inlineStr">
+        <is>
+          <t>SASA Gold, ISO 9001, Level 1 B-BBEE certified. 30+ years in market. Services: Armed Reaction, Physical Guarding, Remote Monitoring, Smart Surveillance, Drone Force. Also runs 24/7 Drone Force — autonomous drones for residential estate perimeter security. PSIRA registration: 70152. Offices: JHB, Tshwane, Cape Town. Ice-breaker: 24/7 Drone Force expansion into autonomous perimeter security.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Oliver Wyman Forum</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>John Romeo</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Managing Partner &amp; CEO, Oliver Wyman Forum</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>owforum@oliverwyman.com</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.oliverwymanforum.com/</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/oliverwymanforum/about/</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>New York, USA</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>Management Consulting / Think Tank</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>Organic/Manual</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>Pending Send</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>OliverWymanForum_Pitch_GenosAI.pptx</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t>AI-powered executive community management (invitation, onboarding, engagement sequences for CEO/CFO Leadership Reimagined community); research distribution automation with audience segmentation for reports and Uncharted weekly insights; event and convening coordination AI (registration, reminders, post-event follow-ups, speaker management); member qualification flow for Leadership Reimagined applicants; CRM automation for C-suite relationship touchpoints; content distribution AI for research publications across LinkedIn and email</t>
+        </is>
+      </c>
+      <c r="Q19" s="3" t="inlineStr">
+        <is>
+          <t>Think tank arm of Oliver Wyman (part of Marsh McLennan). CEO Agenda 2026 covers 10% of global market cap. CFO Agenda 2026 covers 12% of global market cap. Leadership Reimagined is exclusive CEO community. 'Uncharted' is their weekly data-driven insights series. Global Consumer Sentiment Survey reaches 300K+ respondents. Ice-breaker: CEO Agenda 2026 scale — managing relationships at 10% of global market cap is a community-management infrastructure problem. Personal LinkedIn not found — used Forum activity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>AndCo Realty Group</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Jason Clark</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Director &amp; Co-Founder</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>jason@andcorealty.nz</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>+64 274 838 808</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.andcorealty.nz/</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/andco-realty-group/about/</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>Real Estate</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>Organic/Manual</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>Pending Send</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>AndCoRealty_Pitch_GenosAI.pptx</t>
+        </is>
+      </c>
+      <c r="P20" s="3" t="inlineStr">
+        <is>
+          <t>Agent/franchisee onboarding automation via WhatsApp (compliance orientation, marketing setup, milestone check-ins for new office operators); WhatsApp AI for buyer inquiry routing to the right regional office by area and property type; vendor nurture sequences for sellers who requested appraisal but haven't listed; REAA compliance and CPD tracking per agent across 17 offices with automated renewal reminders; post-settlement review collection automation; agent performance reporting delivered monthly to each franchisee automatically</t>
+        </is>
+      </c>
+      <c r="Q20" s="3" t="inlineStr">
+        <is>
+          <t>Fixed-fee commission model. 17 independent offices across NZ (Dunedin, Queenstown, Taranaki, Bay of Plenty, Whanganui, Wellington). Agent-owned franchise model — 'Your company, you call the shots.' Residential focus $500K-$5M+. REAA 2008 licensed. Co-founders: Jason Clark (Director), Kelly Clark (Business Development), Craig Lowe (Director). Personal LinkedIn not found — ice-breaker from website model/scale.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>JamesEdition</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Eric Finnas Dahlstrom</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>info@jamesedition.com</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>+31 20 241 7944</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.jamesedition.com/</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/jamesedition/</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>North Holland, Netherlands</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>Luxury Marketplace / PropTech</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>Organic/Manual</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>Pending Send</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>JamesEdition_Pitch_GenosAI.pptx</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t>Seller onboarding automation (structured WhatsApp/email sequences for new sellers — listing optimization, platform guidance, milestone check-ins); churn prevention AI (flag sellers with no leads in 14+ days and trigger re-engagement before cancellation); upsell trigger sequences (basic to premium based on lead volume); buyer inquiry pre-qualification for $500K+ listings; tier-1 support automation (account, billing, listing queries handled by AI); seller performance report delivery (automated monthly dashboards to each seller)</t>
+        </is>
+      </c>
+      <c r="Q21" s="3" t="inlineStr">
+        <is>
+          <t>Global luxury marketplace. 770K+ listings, 40K+ sellers, 21K+ trusted sellers, 120+ countries, 35 employees. Subscription model: $299-$1,199/month. Min listing price $500K USD. Founder: Noam Perski. CEO: Eric Finnas Dahlstrom (prev. Head of General Classifieds at Avito). CTO: Alexander Lomakin. Categories: real estate, yachts, jets, cars, watches. Tech stack: Pipedrive CRM, Hotjar, Mixpanel, Tableau. Ice-breaker: 35-person team managing 40K+ sellers across 120 countries — operational ratio only works with automation. Personal LinkedIn not found.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Reve Real Estate / Riversong Technology</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Haitham Kalakesh</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Founder &amp; CEO</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>info@riversongtechnology.com</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>+971 4 583 9860</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>https://reverealestates.com/home</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/haithamkalakesh/</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>Real Estate / Consumer Electronics</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>Organic/Manual</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>Pending Send</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>HaithamKalakesh_Audit_GenosAI.pptx</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="inlineStr">
+        <is>
+          <t>Reve Real Estate: property inquiry AI via WhatsApp and web chat (capture name, budget, property type, timeline before agent involvement); investor nurture sequences for leads who enquired but did not book a viewing; Golden Visa consultation funnel (education sequence to qualified call); developer launch alerts to buyer database. Riversong Technology: distributor and retailer B2B inquiry routing AI; customer support automation for product queries, warranty, and returns; post-purchase review and warranty registration sequences; B2B partnership qualification flow for new market entry. Cross-business: unified CRM pipeline and executive reporting AI covering both companies for Haitham.</t>
+        </is>
+      </c>
+      <c r="Q22" s="3" t="inlineStr">
+        <is>
+          <t>Dual-founder profile: Reve Real Estate (reverealestates.com) — Dubai HQ, offices in London, Beirut, Amman. Services: property sales, management, investment, Golden Visa consultation. Developer partners: Emaar, Damac, Meraas, Select Group, Ellington, Majid Al Futtaim. Website score 3/10 (CRITICAL — no chat, no booking, no lead capture, no reviews, no visible contact). Riversong Technology (riversongtechnology.com) — consumer electronics: smart watches, earbuds, phones, smart TVs, ACs. Dubai JLT X3 Tower, London, Cairo. VP Levant: Mutasem Shehadeh. Website score 6/10 (no chat, no WhatsApp, no reviews). Ice-breaker: running two distinct businesses (luxury real estate + consumer electronics) from Dubai across 5+ markets is an unusual operational profile. Personal LinkedIn found but inaccessible (HTTP 999).</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Education Outcomes Fund (EOF)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Dr. Amel Karboul</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>amel.karboul@educationoutcomesfund.org</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr"/>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.educationoutcomesfund.org/</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/the-education-outcomes-fund/</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>England, UK</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>Education / Impact Finance / NGO</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>Organic/Manual</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>Pending Send</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>EducationOutcomesFund_Audit_GenosAI.pptx</t>
+        </is>
+      </c>
+      <c r="P23" s="3" t="inlineStr">
+        <is>
+          <t>Partner and implementer intake AI (smart triage and routing for NGO/government/investor proposals currently submitted via a generic Google Form); donor reporting automation (auto-generate verified outcomes reports per donor from program data -- CIFF, UBS Optimus, Japan MoFA each have different requirements); stakeholder communications AI (segmented newsletter/update sequences by audience: government partner, donor, implementer, researcher); knowledge management RAG system (searchable AI layer over EOF's published practice notes, case studies, and technical briefs); country team coordination AI (async update summaries and scheduling automation for Sierra Leone, Nigeria, Rwanda, South Africa, Tunisia, Namibia teams); meeting scheduling automation (Calendly-style booking replacing single contact form for inbound donor and partner calls)</t>
+        </is>
+      </c>
+      <c r="Q23" s="3" t="inlineStr">
+        <is>
+          <t>Founded 2018. Hosted by UNICEF. Founded by Education Commission + Global Steering Group for Impact Investing. Mission: outcomes-based education financing -- payment tied to verified learning/enrollment/employment results. ~45 staff, London HQ. Active programs: Sierra Leone (SLEIC, $18M, 100K+ children), Nigeria LEAF ($25M, 200K children, launched March 2026), Rwanda (ECD), South Africa, Tunisia (youth employment). Namibia in development (government committed $6M+). $130M+ mobilized. 500K+ beneficiaries. 2030 goal: 15 partnerships, 2M children, $350M. Board: Sir Ronald Cohen (Chair), Jakaya Kikwete, David Sengeh. Deputy CEO: Max McCabe. Chief Programmes Officer: Milena Castellnou. Head of Development: Eugenio Donadio. 19,581 LinkedIn followers. Website built on Wix -- limited automation capability. Ice-breaker: LEAF Nigeria launch quote (March 2026): 'Real change happens when we stop paying for promises and start paying for results.' 5 active programs managed by 45 people -- operational ratio only works with automation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Regnum Properties</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Laud Morgan Asante</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>info@theregnumproperties.com</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>+233 50 863 5479</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.theregnumproperties.com</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/regnum-properties/</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Accra</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>Greater Accra, Ghana</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>Real Estate / Property Development</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>Organic/Manual</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>Pending Send</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>RegnumProperties_Pitch_GenosAI.pptx</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="inlineStr">
+        <is>
+          <t>Lead qualification AI via WhatsApp (capture budget, property type, timeline, location preference before agent involvement -- critical for diaspora/international buyers enquiring across time zones); investor nurture sequences (automated email/WhatsApp drip for overseas buyers: construction progress updates, payment plan details, market context, viewing booking); social media and content AI (LinkedIn and Instagram content generation -- market insights, project updates, buyer guides -- to grow from 2 followers organically); AI property inquiry chatbot on website with 24/7 availability for diaspora buyers; CRM pipeline automation (automated deal stage tracking, follow-up reminders, buyer communication history -- replacing manual WhatsApp/email tracking)</t>
+        </is>
+      </c>
+      <c r="Q24" s="3" t="inlineStr">
+        <is>
+          <t>Founded 2023. East Legon, Accra, Ghana. CEO: Laud Morgan Asante (BA Political Science/Sociology, U of Ghana; MA International Relations, Webster University St. Louis). Finance Director: Maxwell Addo (48 yrs experience). Active projects: The Alexandria (4.5BR smart townhouses, Trasacco Phase 1 area) and The Arlington (3.5BR, 5-unit gated community). Explicitly targets diaspora/international buyers. Smart home features in all units. No CRM, no WhatsApp button, no virtual tour, no booking system. Website on SitePad/Estatik (placeholder content still live on About page). LinkedIn: 2 followers. Phone: +233 50 863 5479 / +233 (0)302 547 951. Ice-breaker: CEO's MA International Relations background shaped the diaspora buyer thesis -- bridging Ghanaian diaspora investors to luxury Accra developments.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:Q1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1983,7 +2560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2547,29 +3124,380 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Kaden Investment</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>General Enquiries</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="n"/>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>kaden-sa.com serves Saudi HNW investors in Squarespace Arabic — Vision 2030's buyers expect more</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Hi team,
+I went through kaden-sa.com this week. The portfolio positioning — Mixed-Use, Logistics, Retail, Waterfront, Commercial — maps directly to Saudi Arabia's Vision 2030 construction pipeline. The fundamentals are strong.
+Three gaps that will cost leads as Vision 2030 accelerates:
+1. Mobile performance is 44/100. Saudi HNW buyers and institutional partners browse on mobile first. A 4+ second page load on kaden-sa.com hands those visitors to competitors before the Arabic content even renders.
+2. The Arabic-English parity is incomplete. Arabic pages carry the full story; English pages don't. Overseas investors — the exact profile that Vision 2030 is attracting — hit incomplete content and leave. That's a direct trust deficit for a SAR 289K+ project inquiry.
+3. There is no AI chatbot, no bilingual enquiry handling, and no automated investor follow-up. A Saudi HNW buyer browsing at 11pm doesn't wait for an email reply the next morning. The developer that responds immediately in Arabic — through an AI agent — wins the appointment.
+We build AI systems for exactly this: a bilingual (AR/EN) AI agent on kaden-sa.com, investor and tenant portals with Azure AD authentication, automated Vision 2030 market intelligence reports, and an Algolia-powered bilingual property search. PDPL cookie consent is a one-day fix that removes the data protection exposure.
+I put together a 12-slide audit deck specific to Kaden — PageSpeed targets, bilingual AI agent spec, investor portal scope, and a phased roadmap with indicative SAR pricing.
+Happy to send it over or take 15 minutes on a call.
+Worth a conversation?
+Rohan Malik
+CEO, Genos AI
+hello@genosai.tech | +91 638-714-2699
+www.genosai.tech</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Hi team,
+Following up on my message from last week.
+One data point: Saudi Arabia's Vision 2030 construction pipeline is accelerating, and bilingual digital infrastructure is now a procurement-level requirement for major institutional partners. Developers with Arabic AI agents and investor portals are qualifying larger transactions — and faster.
+The audit deck I mentioned covers exactly what's needed on kaden-sa.com. Happy to send it across.
+Rohan
+Genos AI | hello@genosai.tech</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Hi team,
+Last note from me on this.
+If the timing isn't right, no problem. The deck is ready whenever the conversation is — just reply and I'll send it across.
+Rohan
+Genos AI | hello@genosai.tech</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>NewExGen (Pty) Ltd</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Sales / Marketing Team</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="n"/>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>You're a Zoho partner — the AI layer on top of it is the fastest win on your roadmap</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Hi team,
+I spent time on newexgen.co.za this week. 15 years, six service segments, Zoho Bookings live, CRM and Desk in place — the operational foundation is genuine. For an ICT transformation consultancy, the website undersells what the business actually does.
+Three things that stood out:
+1. Mobile PageSpeed is 51/100. You're pitching digital transformation to corporate clients and government departments — and your own site loads slowly on mobile. That's a first-impression inconsistency that procurement teams notice.
+2. The demo booking flow breaks on mobile. Zoho Bookings is live but the booking path misfires on small screens — the exact journey a prospective client would take after seeing a LinkedIn post or a referral.
+3. Zoho SalesIQ's Zia AI is sitting unused. As a Zoho partner with CRM, Desk, and SalesIQ already deployed, you're one configuration away from a 24/7 lead qualification agent that responds to inbound enquiries, books demos automatically, and scores leads in CRM before a human sees them. That's not a new tool purchase — it's switching on what you already have.
+We build AI systems for Zoho-native businesses: Zia AI chatbot activation, AI-scored lead routing in CRM, AI ticket triage and SLA-breach prediction in Zoho Desk, and automated field-technician dispatch for managed services. The POPIA cookie consent and mobile booking fix are both same-day items.
+I put together a 12-slide audit deck specific to NewExGen — Zoho fast-wins, mobile UX fixes, and a phased roadmap with ZAR pricing.
+Happy to send it over or take 15 minutes on a call.
+Worth a conversation?
+Rohan Malik
+CEO, Genos AI
+hello@genosai.tech | +91 638-714-2699
+www.genosai.tech</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>Hi team,
+Following up on my message from last week.
+The fastest win here isn't a new system — it's activating Zia AI on your existing Zoho stack. For a Zoho partner already running CRM, Desk, and SalesIQ, this typically takes under a week and immediately improves lead response time and demo booking conversion.
+Audit deck is ready. Happy to send it across.
+Rohan
+Genos AI | hello@genosai.tech</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Hi team,
+Last note from me.
+If the timing isn't right, I'll leave the deck available whenever it's useful. Just reply and I'll send it over.
+Rohan
+Genos AI | hello@genosai.tech</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Realtor CoJo (RC Realtor)</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>General Enquiries</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="n"/>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>rc-realtor.vercel.app is invisible to Google — a custom domain fixes it in one day</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Hi team,
+I came across RC Realtor while researching Lagos property platforms. The luxury and affordable property positioning — targeting the Lagos market across both segments — is a smart differentiation play.
+One critical issue that will block all growth until it's fixed: rc-realtor.vercel.app is a staging URL. Google treats staging subdomains as non-indexable. Combined with the Next.js CSR-only rendering, the current build returns effectively zero SEO-indexable content — the site title is the only thing Google can read. A buyer searching "luxury apartments Lagos" will never find RC Realtor, regardless of how good the listings are.
+Three things that unblock the business:
+1. Custom domain + branded email. Moving off vercel.app to a proper domain costs under $20/year and immediately signals credibility to Lagos HNW buyers who check whether the agency exists before making a call.
+2. Next.js SSR/SSG migration. Server-side rendering makes every property listing indexable by Google. This is the single highest-ROI move — it turns a site that ranks for nothing into one that can rank for "2-bed Lekki apartment" within 60 days.
+3. WhatsApp CTA on every listing. Lagos buyers don't fill out contact forms — they tap WhatsApp. A click-to-chat button on each listing, backed by an AI agent that qualifies budget and books viewings, captures the leads the current site is losing every day.
+We build AI systems for exactly this: custom domain setup, SSR migration via Next.js 15 with Sanity CMS, WhatsApp AI agent for 24/7 lead qualification, and automated listing posts to Instagram and LinkedIn.
+I put together a 12-slide audit deck specific to RC Realtor — SSR migration scope, WhatsApp AI agent flow, and a phased roadmap with NGN/USD pricing.
+Happy to send it over or take 15 minutes on a call.
+Worth a conversation?
+Rohan Malik
+CEO, Genos AI
+hello@genosai.tech | +91 638-714-2699
+www.genosai.tech</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>Hi team,
+Following up on my message from last week.
+The domain + SSR migration point is worth repeating: as long as RC Realtor is on rc-realtor.vercel.app, it cannot rank on Google — regardless of listing quality or marketing spend. That's a fixable constraint, typically resolved in under 2 weeks.
+Audit deck is ready. Happy to send it over.
+Rohan
+Genos AI | hello@genosai.tech</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Hi team,
+Last one from me.
+If the timing isn't right, no problem. The deck is there when you need it — just reply and I'll send it across.
+Rohan
+Genos AI | hello@genosai.tech</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Idili Africa</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>General Enquiries</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="n"/>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>SA graduates placed in Sweden — and the candidate pipeline is a 4-page website</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Hi team,
+I spent time on idili.africa this week. The mission — routing South African graduates (18–25) into Saab, Atlas Copco, and Swedish partner companies — is a genuinely differentiated offer in the graduate recruitment space. The Oakvale Invest and Sweden Consulate Cape Town affiliations are strong proof of concept.
+The infrastructure doesn't match the ambition.
+Three things that are limiting growth right now:
+1. The site is four pages with fragile URLs that 404 mid-navigation. A prospective graduate who clicks through from your LinkedIn post and hits a broken page doesn't apply — they close the tab. With no ATS or candidate portal, there's no other way to capture that interest.
+2. There is no candidate tracking system. When a graduate submits interest, what happens next? Without an ATS, every step from application to shortlist to partner match to placement is manual. That process doesn't scale to the volume Idili Africa needs to be credible to partners like Saab.
+3. The opportunity listings have no SEO structure. A graduate searching "graduate jobs South Africa Sweden" or "international placement programme SA" will never find idili.africa — the current site has no JobPosting schema and virtually no indexable content.
+We build AI systems for exactly this: a candidate intake portal with CV parsing and AI skills extraction, an automated WhatsApp candidate journey (eligibility check → document upload → assessment booking → status updates), a partner dashboard for Saab and Atlas Copco, and SEO-optimised opportunity listings that rank on Google.
+I put together a 12-slide proposal specific to Idili Africa — ATS scope, candidate AI flow, partner portal spec, and a phased roadmap with ZAR/USD pricing.
+Happy to send it over or take 15 minutes on a call.
+Worth a conversation?
+Rohan Malik
+CEO, Genos AI
+hello@genosai.tech | +91 638-714-2699
+www.genosai.tech</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>Hi team,
+Following up on my note from last week.
+The ATS gap is the most immediate constraint — without a candidate tracking system, Idili Africa's growth is bottlenecked by manual coordination. An AI-assisted intake portal that parses CVs and auto-qualifies graduates against partner requirements is the single fastest unlock.
+Proposal is ready. Happy to send it across.
+Rohan
+Genos AI | hello@genosai.tech</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Hi team,
+Last note from me.
+If the timing isn't right, no problem. The proposal is ready whenever the conversation is useful — just reply and I'll send it across.
+Rohan
+Genos AI | hello@genosai.tech</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Shalom Park Estate (IFT Realty Ltd)</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Oluremi Oshikanlu</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="n"/>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Shalom Park: luxury Lekki units with no pricing on the website — diaspora buyers won't call</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Hi Oluremi,
+I went through shalomparknigeria.com this week. 25 acres, Lekki-Epe axis, Lagos State Governor's Consent, Megacity Plan approval — the legal foundation for Shalom Park is stronger than most Nigerian luxury developments I've reviewed.
+Three things are directly blocking diaspora conversions:
+1. There is no pricing on the website. Not a starting figure, not a "from ₦X" marker, not a USD equivalent. A US or UK Nigerian browsing at 11pm New York time will not fill out a contact form to ask what a 4-bed semi-detached costs — they'll move to the next developer who shows numbers. In the diaspora market, hiding pricing signals uncertainty.
+2. There is no WhatsApp CTA on any listing. Nigerian and diaspora buyers use WhatsApp before they use anything else. A "Chat on WhatsApp" button on every unit page — backed by an AI agent that sends brochures, answers questions on unit type, and books site visits — captures the inquiry before it goes to a competitor.
+3. The realtor onboarding runs on Google Meet. For a developer positioning at luxury price points, sending partner realtors through a generic video call for onboarding is a brand mismatch. A dedicated realtor portal with commission tracking, marketing collateral downloads, and automated lead assignment signals the professionalism that attracts top Lagos agents.
+We build AI systems for exactly this: a WhatsApp AI agent for 24/7 buyer qualification, automated diaspora investor sequences (US/UK Nigerians in USD), a partner realtor portal, and monthly construction progress automations that keep buyers warm from deposit to handover.
+I put together a 12-slide audit deck specific to Shalom Park — pricing strategy, diaspora buyer journey, realtor portal scope, and a phased roadmap with NGN/USD pricing.
+Happy to send it over or take 15 minutes on a call.
+Worth a conversation?
+Rohan Malik
+CEO, Genos AI
+hello@genosai.tech | +91 638-714-2699
+www.genosai.tech</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>Hi Oluremi,
+Following up on my message from last week.
+The pricing gap is the single fastest thing to fix — adding "from ₦X / from $X" to each unit page typically increases diaspora inquiry conversion by 30–40% within the first month. Everything else builds on that.
+Audit deck is ready. Happy to send it across.
+Rohan
+Genos AI | hello@genosai.tech</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Hi Oluremi,
+Last one from me.
+If the timing isn't right, no problem. The deck covers pricing strategy, diaspora buyer flows, and the realtor portal in full — I'll leave it available whenever the conversation is useful.
+Rohan
+Genos AI | hello@genosai.tech</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Fortress Real Estate Investments Limited</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Steven Brown</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="n"/>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>R29.6B REIT, JSE-listed — and fortressfund.co.za is invisible to institutional screeners</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Hi Steven,
+I spent time on fortressfund.co.za this week. R29.6B market cap, 2.9M sqm GLA, 52 retail centres, logistics across SA and Central Eastern Europe, 23.9% stake in NEPI Rockcastle — the portfolio is among the most diversified in the JSE REIT universe.
+The digital infrastructure doesn't reflect the scale.
+Three specific issues:
+1. fortressfund.co.za is a JavaScript-rendered SPA. Institutional ESG screeners, Bloomberg terminal plugins, and JSE data aggregators that parse pages programmatically see nothing — the content is invisible until JavaScript executes, which automated tools typically don't wait for. Every SENS announcement, property listing, and ESG disclosure in the current build is effectively unindexed by the tools that institutional investors actually use.
+2. The IR experience lags global REIT peers. Growthpoint, Redefine, and Emira all publish SENS feeds, live share-price widgets, and one-click dividend history on their IR pages. Fortress's equivalent requires investors to navigate multiple clicks with no live data surface. For FFA and FFB holders, that friction is a retention and engagement gap.
+3. There is no AI layer on the investor or leasing side. An IR chatbot trained on Fortress SENS filings, annual reports, and dividend history would handle 80% of analyst inquiries — NAV per unit, yield calculations, lease expiry profiles — without management time. On the leasing side, a searchable GLA availability portal that qualifies inbound tenants before your BD team engages would materially reduce time-to-lease on logistics vacancies.
+We build AI systems for institutional-grade real estate platforms: SSR migration to Next.js 15 (making every page Google and Bloomberg-indexable), a live IR hub with SENS aggregation and share-price tickers, an IR chatbot trained on Fortress filings, a logistics and retail leasing portal, and ESG dashboard automation for TCFD/GRESB submissions.
+I put together a 14-slide proposal specific to Fortress — SSR migration scope, IR hub spec, AI chatbot training data plan, and a phased roadmap with indicative ZAR pricing.
+Happy to send it over or take 20 minutes on a call.
+Worth a conversation?
+Rohan Malik
+CEO, Genos AI
+hello@genosai.tech | +91 638-714-2699
+www.genosai.tech</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>Hi Steven,
+Following up on my message from last week.
+The SSR migration point is worth underlining: as long as fortressfund.co.za runs as a JS-rendered SPA, every piece of content — SENS filings, property data, ESG disclosures — is invisible to the programmatic tools institutional investors and screeners rely on. That's a resolvable infrastructure gap, typically addressed in 6–8 weeks for a site of this scope.
+Proposal is ready. Happy to send it across.
+Rohan
+Genos AI | hello@genosai.tech</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Hi Steven,
+Last note from me.
+If the timing isn't right, no problem. The proposal covers the IR hub, AI chatbot, leasing portal, and ESG automation in full — available whenever the conversation is useful.
+Rohan
+Genos AI | hello@genosai.tech</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Home Seekers</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>Thomas Potgieter</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>info@homeseeker.co.za</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>416 listings and buyer inquiries waiting while agents are at viewings</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>Hi Thomas,
 Saw the LinkedIn post on Rode's October run — 8 deals for R11.44M on a 100%-commission model. That number makes the platform's value proposition more credible than any recruitment copy.
@@ -2585,42 +3513,42 @@
 +91 638-714-2699  |  hello@genosai.tech  |  www.genosai.tech</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G16" s="3" t="inlineStr">
         <is>
           <t>Hi Thomas, following up on my last message. The core gap — buyer inquiries on your 416 listings sitting unanswered while agents are at viewings — is the fastest to close. A WhatsApp AI agent for Home Seekers is typically live in under 2 weeks. Happy to walk through it in 20 minutes. — Rohan | Genos AI</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="H16" s="3" t="inlineStr">
         <is>
           <t>Thomas, last one from me. On a 100%-commission platform, an agent's income depends entirely on their lead conversion speed. An AI that ensures no buyer inquiry goes unanswered — even at 9pm on a Sunday — is the infrastructure that makes your agents more productive than any franchise competitor. Leaving this here if the timing isn't right. — Rohan | Genos AI</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="3" t="n">
+    <row r="17">
+      <c r="A17" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>Swisszaco Estates</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E17" s="3" t="inlineStr">
         <is>
           <t>Swisszaco's agent network and a property inquiry process still stuck on contact forms</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F17" s="3" t="inlineStr">
         <is>
           <t>Hi,
 Came across Swisszaco Estates while researching real estate developers in Nigeria. CAC-registered since March 2012 — 13 years in the market across construction, estate development, architectural design, and urban development. The agent network program stood out as an indicator the business is actively scaling.
@@ -2633,14 +3561,376 @@
 +91 638-714-2699  |  hello@genosai.tech  |  www.genosai.tech</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G17" s="3" t="inlineStr">
         <is>
           <t>Hi, following up on my last message. The core gap — property inquiries hitting a static contact form while competitors respond on WhatsApp in minutes — is the fastest thing to fix. A WhatsApp AI agent for Swisszaco is typically live within 2 weeks. Happy to show you exactly how it works in 15 minutes. — Rohan | Genos AI</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="H17" s="3" t="inlineStr">
         <is>
           <t>Last one from me. The Swisszaco audit covers the WhatsApp buyer qualification flow, agent recruitment automation, and the property viewing booking system specifically. If the timing isn't right, no problem — leaving it here in case it's useful later. — Rohan | Genos AI</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>24/7 Security Services</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>David De Lima</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>info@24-7security.co.za</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Security quotes via contact form while residential estates move to instant WhatsApp response</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Hi David,
+Saw the 24/7 Drone Force expansion — autonomous drones reshaping perimeter security in residential estates is a different category from the standard guarding pitch. That kind of operational innovation is hard to replicate.
+One gap that shows up when you look at 24-7security.co.za from a prospect's perspective: someone managing a residential estate or commercial property contacts you for a quote, fills in a form, and waits. Meanwhile they've sent the same inquiry to three other security companies. The first one to respond on WhatsApp — even if it's an AI asking qualifying questions — controls that conversation.
+What Genos AI builds for security companies like 24/7:
+WhatsApp AI for prospect inquiries — responds 24/7, asks qualifying questions (property type, size, current security setup, risk level), routes commercial to commercial and residential to residential, schedules a site assessment automatically.
+Automated quote generation — site assessment inputs trigger a structured quote to your ops team. No manual data entry from the client side.
+Guard attendance and shift automation — shift confirmations via WhatsApp, exception alerts when a guard doesn't check in. PSIRA certification renewal dates tracked per guard with automated reminders — no admin overhead.
+Client communication automation — monthly activity reports and incident summaries delivered automatically to each client account. Makes your service value visible without your team writing reports manually.
+I'm Rohan Malik, CEO of Genos AI. We build AI automation for security companies and managed service businesses. Happy to walk through the inquiry flow in a 20-minute call.
+Rohan Malik
+CEO, Genos AI
++91 638-714-2699  |  hello@genosai.tech  |  www.genosai.tech</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>Hi David, following up on my last message. The fastest fix — a WhatsApp AI that captures and qualifies security quote inquiries 24/7 — is typically live in under 2 weeks. Happy to walk through it in 20 minutes. — Rohan | Genos AI</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>David, last one from me. For a company operating armed reaction across Johannesburg, Tshwane, and Cape Town simultaneously, the complexity of guard scheduling, client reporting, and prospect follow-up adds up fast. AI automation addresses all three without adding headcount. Leaving this here if the timing isn't right. — Rohan | Genos AI</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Oliver Wyman Forum</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>John Romeo</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>owforum@oliverwyman.com</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Leadership Reimagined runs on relationships — the follow-through infrastructure could be automated</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Hi John,
+The CEO Agenda 2026 covering leaders at 10% of global market capitalization is an extraordinary convening mandate. The operational question it raises: maintaining meaningful, consistent touchpoints with that many C-suite relationships — invitations, pre-event briefings, post-event follow-up, research delivery, renewal — is a community-management infrastructure problem at scale. Right now that follow-through depends on who is at their desk.
+Genos AI builds the automation layer for organizations that run on executive relationships. For the Oliver Wyman Forum specifically:
+Executive community management automation — personalized outreach sequences for CEO and CFO community members. Event invitations, pre-reading delivery, post-convening follow-up, and renewal outreach — all triggered by calendar and behavior, not by someone tracking a spreadsheet.
+Research distribution and segmentation — automated delivery of Uncharted insights and Forum reports to audience segments based on stated interests and engagement history. Reports that executives subscribed to but never received a coherent follow-up on.
+Event and convening coordination — automated registration flows, speaker briefing distribution, attendee reminder sequences, and post-event summary delivery. Removes the admin overhead from every convening without reducing quality.
+Member qualification for Leadership Reimagined — when executives express interest in the community, an automated flow qualifies their profile, routes to the right engagement track, and ensures no application sits cold.
+I'm Rohan Malik, CEO of Genos AI. We build AI automation for research-led organizations and executive communities. Happy to show you how it maps to the Forum's workflow in a 15-minute call.
+Rohan Malik
+CEO, Genos AI
++91 638-714-2699  |  hello@genosai.tech  |  www.genosai.tech</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>Hi John, following up on my last message. The most immediate value — automating the follow-up and engagement sequences around your executive convenings — is typically live within 2 weeks. Happy to walk through it in 15 minutes. — Rohan | Genos AI</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>John, last one from me. An organization running CEO and CFO agenda programs at the scale of global market capitalization needs the operational infrastructure to match. AI automation for community management, research distribution, and event follow-through is exactly that infrastructure. Leaving this here if the timing isn't right. — Rohan | Genos AI</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>AndCo Realty Group</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Jason Clark</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>jason@andcorealty.nz</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>17 independent offices — onboarding, compliance, and lead flow for each without scaling your team</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Hi Jason,
+The AndCo model — fixed-fee, agent-owned, 17 offices across New Zealand — is a structurally different proposition to any traditional franchise. The operational challenge it creates is specific: every new office operator needs the same quality of onboarding, compliance guidance, and lead flow, but the team delivering that support doesn't scale linearly with the number of offices.
+Genos AI builds the automation layer for real estate groups at this stage. For AndCo specifically:
+Agent onboarding automation — new office operators go through a structured WhatsApp-based flow: compliance orientation, marketing setup, listing platform training, and milestone check-ins. You set the content once; the AI runs it for every new operator from day one.
+Buyer inquiry routing — a WhatsApp AI that qualifies buyer inquiries from the AndCo website and routes them to the right regional office by area and property type. Each agent receives a pre-qualified lead with budget, property type, and timeline already captured.
+Vendor nurture sequences — sellers who request an appraisal but don't proceed immediately receive an automated follow-up over 6-12 weeks. The agent stays top of mind without tracking every warm prospect manually.
+REAA compliance and CPD tracking — license renewal dates and CPD requirements tracked per agent across all 17 offices, with automated reminders at 90, 30, and 7 days. No agent falls out of compliance because a reminder was missed.
+Post-settlement review collection — automated Google and Trade Me review requests at settlement date. Across 17 offices, that's consistent social proof built without any admin overhead.
+I'm Rohan Malik, CEO of Genos AI. We build AI automation for real estate groups. Happy to show you how it maps to AndCo's model in 20 minutes.
+Rohan Malik
+CEO, Genos AI
++91 638-714-2699  |  hello@genosai.tech  |  www.genosai.tech</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>Hi Jason, following up on my last message. The fastest fix for a group at AndCo's stage — automating the onboarding flow for new office operators so your team isn't manually running the same process every time — is typically live in under 2 weeks. Happy to walk through it in 20 minutes. — Rohan | Genos AI</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>Jason, last one from me. A fixed-fee model with 17 independent offices scales on agent trust and operational consistency. AI automation ensures every new office operator gets the same quality of onboarding and support — regardless of how many join in a given month. Leaving this here if the timing isn't right. — Rohan | Genos AI</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>JamesEdition</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Eric Finnas Dahlstrom</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>info@jamesedition.com</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>35 employees, 40,000 sellers, 120 countries — the operational ratio that only works with automation</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Hi Eric,
+JamesEdition runs 40,000+ sellers across 120 countries with a 35-person team. That ratio only works because the platform handles discovery — but the seller-side operational layer (onboarding, engagement, churn prevention, upsell) scales differently from the marketplace itself.
+The gap at JamesEdition's current stage: a seller paying $299/month who doesn't see inquiries in week one is likely to cancel. A seller on a basic plan who's getting strong lead volume has no automated prompt to upgrade to premium. Neither problem requires a human — both require a system.
+What Genos AI builds for marketplace businesses at JamesEdition's scale:
+Seller onboarding automation — new sellers receive a structured sequence: listing optimisation guidance, platform tips, performance benchmarks, and milestone check-ins. With 40,000 sellers and 35 employees, that process doesn't happen manually — and most sellers who leave in month one leave because nobody helped them get started.
+Churn prevention AI — sellers whose lead volume drops below a threshold, or who haven't logged in for 14 days, are flagged and receive an automated re-engagement sequence before they cancel. At $299–$1,199/month per seller, each prevented cancellation is material to revenue.
+Upsell trigger sequences — sellers on basic plans who've received strong lead volume receive an automated upgrade prompt with specific ROI context from their own data. No sales rep required.
+Buyer pre-qualification — when a buyer inquires on a $5M+ listing, an AI runs an initial qualification (budget confirmed, timeline, finance or cash) before connecting to the seller. Reduces seller time spent on unqualified inquiries — a common complaint on luxury platforms.
+Tier-1 support automation — listing issues, account questions, billing queries handled by AI before escalating to your team. With 21,000+ trusted sellers, the inbound support volume doesn't scale to 35 people without automation.
+I'm Rohan Malik, CEO of Genos AI. We build AI automation for marketplace businesses. Happy to show you how it maps to JamesEdition's operational model in 15 minutes.
+Rohan Malik
+CEO, Genos AI
++91 638-714-2699  |  hello@genosai.tech  |  www.genosai.tech</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>Hi Eric, following up on my last message. The highest-impact fix — churn prevention sequences for sellers who go quiet in the first 30 days — is typically live in under 2 weeks and directly protects subscription revenue. Happy to walk through it in 15 minutes. — Rohan | Genos AI</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Eric, last one from me. A 35-person team running a $299–$1,199/month subscription marketplace at 40,000+ sellers across 120 countries only stays profitable if the seller success layer is automated. That's exactly what we build. Leaving this here if the timing isn't right. — Rohan | Genos AI</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Reve Real Estate / Riversong Technology</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Haitham Kalakesh</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>info@riversongtechnology.com</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Two Dubai businesses, one missing layer — AI automation for Reve Real Estate and Riversong Technology</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Hi Haitham,
+Running two distinct businesses from Dubai -- a luxury real estate portal operating across Dubai, London, Beirut, and Amman, and a consumer electronics brand distributed across the Middle East and beyond -- means two separate inquiry pipelines, two support channels, and two sets of leads that currently depend on manual follow-up.
+The gap in both businesses is the same: someone inquires, and without a structured automation layer, the follow-up quality depends entirely on who picks it up and when.
+What Genos AI builds for each:
+For Reve Real Estate:
+Property inquiry AI -- a WhatsApp and web chat flow that captures budget, property type, location preference, and timeline before the agent is involved. Emaar, Damac, and Meraas developers bring serious buyer traffic; that traffic needs qualification before it reaches your team.
+Investor nurture sequences -- leads who submitted an inquiry but didn't book a viewing receive a structured follow-up over 4--6 weeks: market data, featured projects, and a re-engagement prompt. Most real estate deals close on the fourth or fifth follow-up, not the first.
+Golden Visa consultation funnel -- an automated education sequence for international investors asking about UAE residency through property investment. Qualified leads routed to a consultation call; unqualified leads nurtured until ready.
+For Riversong Technology:
+Distributor and retailer inquiry routing -- a B2B inquiry AI that qualifies new distribution or retail partnership enquiries by region, category, and order volume before connecting to your sales team.
+Customer support automation -- product questions, warranty claims, and return requests handled by AI for the consumer side. With a product range across smart watches, earbuds, TVs, and ACs, the support query volume doesn't scale manually.
+I'm Rohan Malik, CEO of Genos AI. We build AI automation for businesses operating at this kind of operational scale. Happy to show you how it maps to both companies in 20 minutes.
+Rohan Malik
+CEO, Genos AI
++91 638-714-2699  |  hello@genosai.tech  |  www.genosai.tech</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>Hi Haitham, following up on my last message. The fastest win for Reve Real Estate -- a WhatsApp inquiry AI that pre-qualifies buyers before they reach your agents -- is typically live in under 2 weeks and directly protects agent time on your highest-value listings. Happy to walk through it in 20 minutes. -- Rohan | Genos AI</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Haitham, last one from me. Two businesses across real estate and consumer electronics, both operating across multiple markets, both with inquiry pipelines that scale only as far as the team managing them. That is exactly the problem AI automation solves. Leaving this here if the timing is not right. -- Rohan | Genos AI</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Education Outcomes Fund (EOF)</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Dr. Amel Karboul</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>amel.karboul@educationoutcomesfund.org</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>5 programs, 45 people, $130 million -- the operational layer that does not scale without automation</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Hi Amel,
+EOF launched the Lagos Education Access Fund in March 2026 -- the fifth active Outcomes Partnership in four years, with Namibia in development. That is a 5x growth in programme complexity managed by roughly the same team of 45 people. Your quote at the LEAF launch captures the philosophy precisely: real change happens when you stop paying for promises and start paying for results.
+The principle applies to your operations too. Right now, every inbound partner proposal, donor inquiry, and government engagement arrives through a single generic contact form and is handled manually. At SLEIC scale, that works. At five simultaneous programmes across six countries -- with different donor reporting requirements for CIFF, UBS Optimus, and the Japan MoFA -- it becomes the bottleneck.
+What Genos AI builds for organisations at EOF's stage:
+Partner and implementer intake AI -- inbound proposals from NGOs, governments, and investors currently flow through a Google Form with no automated triage. An AI intake system scores and routes each proposal by programme type, geography, and organisational capacity before a programme manager is involved. Cuts weeks off onboarding.
+Donor reporting automation -- each of your five active programmes has different reporting requirements across multiple funders. An AI layer that aggregates verified outcomes data and auto-generates funder-specific report drafts eliminates the analyst hours currently spent compiling from raw verification data.
+Stakeholder communications AI -- 19,581 LinkedIn followers and a newsletter database with no visible segmentation or automation. Government partners, donors, implementers, and researchers each need different content. Automated sequences for each audience, triggered by role and geography, multiply EOF's reach without adding headcount.
+Knowledge management -- EOF publishes practice notes, case studies, and technical briefs that represent irreplaceable institutional knowledge. A RAG-based AI system over that content base means any team member -- from a new Programme Analyst in Rwanda to a Policy Advisor in London -- can query it in seconds.
+Country team coordination -- with programme leads in Sierra Leone, Nigeria, Rwanda, South Africa, and Tunisia all reporting to London, async update synthesis and automated scheduling reduces coordination overhead for you and Max significantly.
+I'm Rohan Malik, CEO of Genos AI. We build AI automation for mission-driven organisations that need to scale impact without scaling headcount. Happy to show you how it maps to EOF's operational model in 20 minutes.
+Rohan Malik
+CEO, Genos AI
++91 638-714-2699  |  hello@genosai.tech  |  www.genosai.tech</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>Hi Amel, following up on my note. The fastest win for EOF -- an AI intake and routing system for the partner and implementer proposals currently coming through a generic Google Form -- is typically live in under 2 weeks and directly reduces programme team time on unqualified enquiries. Happy to walk through it in 20 minutes. -- Rohan | Genos AI</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>Amel, last one from me. Five active Outcomes Partnerships across six countries, managed by 45 people, with Namibia in development -- that ratio only holds if the operational layer is automated. That is exactly what we build. Leaving this here if the timing is not right. -- Rohan | Genos AI</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Regnum Properties</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Laud Morgan Asante</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>info@theregnumproperties.com</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>The Arlington, 5 units, diaspora buyers -- the automation layer that converts overseas interest before it goes cold</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Hi Laud,
+Regnum Properties is built around a specific thesis: luxury residential developments in East Legon sold to international buyers and the Ghanaian diaspora. That thesis is commercially strong -- diaspora demand for Accra real estate is real and growing. The challenge it creates is operational: a buyer in London or Atlanta sees The Arlington at 10 PM their time, fills in a contact form, and by the time someone picks it up Monday morning, the moment is gone.
+The gap between international interest and signed deals is almost always a follow-up problem. Not a product problem.
+What Genos AI builds for real estate developers at Regnum's stage:
+WhatsApp lead qualification AI -- a WhatsApp number displayed on the Regnum website and social profiles handles inbound enquiries automatically: budget, property type preference, timeline, and location interest captured before any agent is involved. A diaspora buyer in Toronto can qualify themselves at midnight and wake up to a confirmed viewing booking.
+Investor nurture sequences -- buyers who enquire but do not convert immediately enter an automated sequence: construction progress photos, payment plan breakdowns, Accra market context, testimonials. The sequence runs for 12 weeks without manual follow-up. Most luxury property deals in Ghana close on the third or fourth contact -- automation ensures those contacts happen.
+Social media content AI -- Regnum is actively posting on LinkedIn and Instagram, which is exactly right. The gap is consistency and volume. An AI layer generates market insight posts, project update content, and diaspora buyer guides on a weekly schedule -- growing an audience without consuming founder time.
+AI property chatbot -- a 24/7 chat widget on theregnumproperties.com that answers property questions, shares floor plans, and books viewings. For a developer selling smart homes, operating on a basic contact form is a credibility gap.
+CRM pipeline automation -- as The Arlington closes and the next project launches, managing buyer conversations across WhatsApp threads and emails stops scaling. Automated pipeline tracking, follow-up reminders, and communication history in one view means Laud and Maxwell always know exactly where every buyer stands.
+I'm Rohan Malik, CEO of Genos AI. We build AI automation for real estate developers. Happy to show you how it maps to Regnum's sales model in 20 minutes.
+Rohan Malik
+CEO, Genos AI
++91 638-714-2699  |  hello@genosai.tech  |  www.genosai.tech</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>Hi Laud, following up on my last message. The fastest win for Regnum -- a WhatsApp AI that qualifies diaspora buyers the moment they enquire, regardless of time zone -- is typically live in under 2 weeks and directly captures the leads that currently go cold over the weekend. Happy to walk through it in 20 minutes. -- Rohan | Genos AI</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Laud, last one from me. A developer targeting international buyers with no WhatsApp qualification, no nurture sequences, and no 24/7 inquiry capture is leaving deals on the table every week. That is exactly what we fix. Leaving this here if the timing is not right. -- Rohan | Genos AI</t>
         </is>
       </c>
     </row>
@@ -2656,7 +3946,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -3121,95 +4411,679 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Home Seekers</t>
+          <t>Kaden Investment</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Thomas Potgieter</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>info@homeseeker.co.za</t>
-        </is>
-      </c>
+          <t>General Enquiries</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="n"/>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Real Estate</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>5.5</v>
+          <t>Real Estate Development &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>4/10</t>
+        </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>Email Pending</t>
+          <t>To Contact</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>Send cold email — pitch AI automation</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr"/>
+          <t>Source decision-maker email via LinkedIn; send audit deck + bilingual AI agent pitch</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>$20,000–$45,000 (bilingual AI agent + investor portal + Vision 2030 market intelligence)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>NewExGen (Pty) Ltd</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Sales / Marketing Team</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="n"/>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>ICT / Digital Transformation &amp; Managed Services</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>5/10</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>To Contact</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>Source Sales/Marketing Director email via LinkedIn; send audit deck — Zoho AI fast-wins pitch</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>$12,000–$28,000 (Zoho AI activation + mobile UX + managed services automation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Realtor CoJo (RC Realtor)</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>General Enquiries</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="n"/>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Real Estate — Luxury &amp; Affordable Properties</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>2/10</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>To Contact</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>Source founder contact via RC Realtor LinkedIn; lead with domain + SSR migration pitch</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>$8,000–$18,000 (Next.js SSR migration + WhatsApp AI agent + SEO rebuild)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Idili Africa</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>General Enquiries</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="n"/>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>International Talent Mobility &amp; Graduate Recruitment</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>3/10</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>To Contact</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>Source founder/Talent Director contact via LinkedIn or idili.africa; send proposal deck — ATS + candidate AI pitch</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>$15,000–$35,000 (candidate portal ATS + AI screening + partner dashboard + SEO)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Shalom Park Estate (IFT Realty Ltd)</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Oluremi Oshikanlu</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="n"/>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Real Estate — Luxury Estate Development</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>4/10</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>To Contact</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>Source Oluremi Oshikanlu email via IFT Realty website or LinkedIn; send audit deck — diaspora buyer flow + pricing pitch</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>$12,000–$28,000 (WhatsApp AI + diaspora campaign + realtor portal + construction update automation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Fortress Real Estate Investments Limited</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Steven Brown</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="n"/>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>REIT — Logistics &amp; Convenience Retail (JSE: FFA &amp; FFB)</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>5/10</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>To Contact</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>Source Steven Brown email via JSE filing / Fortress investor relations page; send proposal deck — IR hub + SSR migration pitch</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>$50,000–$120,000+ (SSR migration + IR hub + AI chatbot + leasing portal — flagship JSE engagement)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Home Seekers</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Thomas Potgieter</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>info@homeseeker.co.za</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Real Estate</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>Email Pending</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>Send cold email — pitch AI automation</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>Swisszaco Estates</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E17" s="3" t="inlineStr">
         <is>
           <t>Real Estate Development</t>
         </is>
       </c>
-      <c r="F11" s="3" t="n">
+      <c r="F17" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G17" s="3" t="inlineStr">
         <is>
           <t>Contact TBD</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="H17" s="3" t="inlineStr">
         <is>
           <t>2026-05-17</t>
         </is>
       </c>
-      <c r="I11" s="3" t="inlineStr">
+      <c r="I17" s="3" t="inlineStr">
         <is>
           <t>Source contact via LinkedIn — send cold email + deck</t>
         </is>
       </c>
-      <c r="J11" s="3" t="inlineStr">
+      <c r="J17" s="3" t="inlineStr">
         <is>
           <t>$3,000 - $6,000</t>
         </is>
       </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>24/7 Security Services</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>David De Lima</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>info@24-7security.co.za</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Security Services</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>Email Pending</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>Send cold email — pitch AI automation</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Oliver Wyman Forum</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>John Romeo</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>owforum@oliverwyman.com</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Management Consulting / Think Tank</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>Email Pending</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>Send cold email — pitch AI automation</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>AndCo Realty Group</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Jason Clark</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>jason@andcorealty.nz</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Real Estate</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>Email Pending</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>Send cold email — pitch AI automation</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>JamesEdition</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Eric Finnas Dahlstrom</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>info@jamesedition.com</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Luxury Marketplace / PropTech</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>Email Pending</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>Send cold email — pitch AI automation</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Reve Real Estate / Riversong Technology</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Haitham Kalakesh</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>info@riversongtechnology.com</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Real Estate / Consumer Electronics</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>Email Pending</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>Send cold email -- pitch AI automation (dual audit)</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Education Outcomes Fund (EOF)</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Dr. Amel Karboul</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>amel.karboul@educationoutcomesfund.org</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Education / Impact Finance / NGO</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>Email Pending</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>Send cold email -- pitch AI automation for NGO operations</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Regnum Properties</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Laud Morgan Asante</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>info@theregnumproperties.com</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Real Estate / Property Development</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>Email Pending</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>Send cold email -- pitch AI automation for diaspora real estate sales</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:J1"/>
